--- a/isolated_excel/Table 2 - Paper vs Current.xlsx
+++ b/isolated_excel/Table 2 - Paper vs Current.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comparison" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Comparison" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Comparison'!$A$1:$E$11</definedName>

--- a/isolated_excel/Table 2 - Paper vs Current.xlsx
+++ b/isolated_excel/Table 2 - Paper vs Current.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Comparison" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comparison" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Comparison'!$A$1:$E$11</definedName>
@@ -484,10 +484,10 @@
         <v>3.48</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>3.495221238938055</v>
+        <v>3.520614035087721</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.01522123893805549</v>
+        <v>0.04061403508772177</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -505,10 +505,10 @@
         <v>3.4</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3.422856966733567</v>
+        <v>3.448521353622169</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.02285696673356696</v>
+        <v>0.04852135362216892</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -526,10 +526,10 @@
         <v>95.39999999999999</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>95.57522123893806</v>
+        <v>95.6140350877193</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.1752212389380645</v>
+        <v>0.21403508771931</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -547,10 +547,10 @@
         <v>4.6</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>4.424778761061947</v>
+        <v>4.385964912280701</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>-0.175221238938053</v>
+        <v>-0.2140350877192985</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -568,10 +568,10 @@
         <v>4.06</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>4.010102220229272</v>
+        <v>4.001514378174758</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>-0.04989777977072762</v>
+        <v>-0.0584856218252412</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -589,10 +589,10 @@
         <v>0.86</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.8716040257792284</v>
+        <v>0.8798204135639283</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.01160402577922837</v>
+        <v>0.01982041356392827</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -610,10 +610,10 @@
         <v>13.96</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>14.35776078315886</v>
+        <v>14.52592048115421</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.3977607831588568</v>
+        <v>0.5659204811542047</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -631,10 +631,10 @@
         <v>88.28</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>92.0046082949309</v>
+        <v>93.47695852534564</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>3.724608294930903</v>
+        <v>5.196958525345636</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
@@ -652,10 +652,10 @@
         <v>3.52</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>3.525269540287813</v>
+        <v>3.553834897000299</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.005269540287813346</v>
+        <v>0.03383489700029907</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -673,10 +673,10 @@
         <v>-0.04</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.02263441138176098</v>
+        <v>-0.02540694158567561</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.01736558861823902</v>
+        <v>0.01459305841432439</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Jan 2017 to May 2026; 113 monthly observations</t>
+          <t>Jan 2017 to Jun 2026; 114 monthly observations</t>
         </is>
       </c>
     </row>

--- a/isolated_excel/Table 2 - Paper vs Current.xlsx
+++ b/isolated_excel/Table 2 - Paper vs Current.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Comparison" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comparison" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Comparison'!$A$1:$E$11</definedName>
@@ -443,7 +443,7 @@
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -484,10 +484,10 @@
         <v>3.48</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>3.520614035087721</v>
+        <v>3.519478260869565</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.04061403508772177</v>
+        <v>0.03947826086956541</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -505,10 +505,10 @@
         <v>3.4</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3.448521353622169</v>
+        <v>3.448012329545969</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.04852135362216892</v>
+        <v>0.04801232954596824</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -526,10 +526,10 @@
         <v>95.39999999999999</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>95.6140350877193</v>
+        <v>95.65217391304348</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.21403508771931</v>
+        <v>0.2521739130434923</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -547,10 +547,10 @@
         <v>4.6</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>4.385964912280701</v>
+        <v>4.347826086956522</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>-0.2140350877192985</v>
+        <v>-0.2521739130434781</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -568,10 +568,10 @@
         <v>4.06</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>4.001514378174758</v>
+        <v>3.983943837120484</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>-0.0584856218252412</v>
+        <v>-0.076056162879516</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -589,10 +589,10 @@
         <v>0.86</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.8798204135639283</v>
+        <v>0.8834156315349503</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.01982041356392827</v>
+        <v>0.0234156315349503</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -610,10 +610,10 @@
         <v>13.96</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>14.52592048115421</v>
+        <v>14.58478488287688</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.5659204811542047</v>
+        <v>0.6247848828768756</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -631,10 +631,10 @@
         <v>88.28</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>93.47695852534564</v>
+        <v>94.25806451612902</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>5.196958525345636</v>
+        <v>5.978064516129024</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
@@ -652,10 +652,10 @@
         <v>3.52</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>3.553834897000299</v>
+        <v>3.552270603645034</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.03383489700029907</v>
+        <v>0.03227060364503354</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -673,10 +673,10 @@
         <v>-0.04</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.02540694158567561</v>
+        <v>-0.02530998899887835</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.01459305841432439</v>
+        <v>0.01469001100112165</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Jan 2017 to Jun 2026; 114 monthly observations</t>
+          <t>Jan 2017 to Jul 2026; 115 monthly observations</t>
         </is>
       </c>
     </row>

--- a/isolated_excel/Table 2 - Paper vs Current.xlsx
+++ b/isolated_excel/Table 2 - Paper vs Current.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comparison" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Comparison" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Comparison'!$A$1:$E$11</definedName>
@@ -484,10 +484,10 @@
         <v>3.48</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>3.519478260869565</v>
+        <v>3.519478260869567</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.03947826086956541</v>
+        <v>0.03947826086956763</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -589,10 +589,10 @@
         <v>0.86</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.8834156315349503</v>
+        <v>0.8834156315349508</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.0234156315349503</v>
+        <v>0.02341563153495085</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -610,10 +610,10 @@
         <v>13.96</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>14.58478488287688</v>
+        <v>14.58478488287689</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.6247848828768756</v>
+        <v>0.6247848828768845</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -631,10 +631,10 @@
         <v>88.28</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>94.25806451612902</v>
+        <v>94.25806451612905</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>5.978064516129024</v>
+        <v>5.978064516129052</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
@@ -652,10 +652,10 @@
         <v>3.52</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>3.552270603645034</v>
+        <v>3.552270603645037</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.03227060364503354</v>
+        <v>0.03227060364503664</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -673,10 +673,10 @@
         <v>-0.04</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.02530998899887835</v>
+        <v>-0.02530998899887851</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.01469001100112165</v>
+        <v>0.01469001100112149</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
